--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>雇主端／職安人員健康管理摘要（Employer Health Management Summary）。落實 security.md 之角色存取控制：雇主僅得取得**健康管理分級、適性配工建議與臨場服務發現**，**不得**取得檢驗數值。以 **closed section slicing** 結構性保證本摘要不含檢驗／影像 section；各 section 之 entry 以 profile 限定，檢驗類 Observation／DiagnosticReport 無從置入。此為欄位級隔離之可驗證機制，取代僅以文字宣示之做法（SMART scope 難達欄位級隔離，見 security.md §2）。存取控制之實作機制（scope／Consent／端點）屬平台端決定，見未決事項 M-10。</t>
+    <t>【依據：勞工健康保護規則附表】雇主端／職安人員健康管理摘要（Employer Health Management Summary）。落實 security.md 之角色存取控制：雇主僅得取得**健康管理分級、適性配工建議與臨場服務發現**，**不得**取得檢驗數值。以 **closed section slicing** 結構性保證本摘要不含檢驗／影像 section；各 section 之 entry 以 profile 限定，檢驗類 Observation／DiagnosticReport 無從置入。此為欄位級隔離之可驗證機制，取代僅以文字宣示之做法（SMART scope 難達欄位級隔離，見 security.md §2）。存取控制之實作機制（scope／Consent／端點）屬平台端決定，見未決事項 M-10。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
+++ b/StructureDefinition-TWHA-Composition-EmployerSummary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
